--- a/benchmarking/results-dist.xlsx
+++ b/benchmarking/results-dist.xlsx
@@ -99,7 +99,7 @@
     <t>rstatus</t>
   </si>
   <si>
-    <t>out of memory</t>
+    <t>out of time</t>
   </si>
   <si>
     <t>status</t>
@@ -1057,9 +1057,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="9" width="11.42578125" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" customWidth="1"/>
-    <col min="11" max="43" width="11.42578125" customWidth="1"/>
+    <col min="2" max="43" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43">
@@ -1258,16 +1256,16 @@
         <v>0</v>
       </c>
       <c r="E3" s="1">
-        <v>3038</v>
+        <v>6369</v>
       </c>
       <c r="F3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I3" s="1">
         <v>0</v>
@@ -1279,7 +1277,7 @@
         <v>21</v>
       </c>
       <c r="L3" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M3" s="1">
         <v>1</v>
